--- a/研究資料/TWSE-2345/正式成果/2345_智邦_估值模型_20261001.xlsx
+++ b/研究資料/TWSE-2345/正式成果/2345_智邦_估值模型_20261001.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估值比較" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kevin模型" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="季度財務" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="來源與缺口" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同業比較" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kevin模型" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="季度財務" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="來源與缺口" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="+0.0;-0.0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -107,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -115,24 +117,39 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,7 +563,7 @@
         <f>Kevin模型!B43</f>
         <v/>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="23">
         <f>B4/Kevin模型!B22-1</f>
         <v/>
       </c>
@@ -566,7 +583,7 @@
         <f>Kevin模型!C43</f>
         <v/>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="23">
         <f>B5/Kevin模型!B22-1</f>
         <v/>
       </c>
@@ -586,7 +603,7 @@
         <f>Kevin模型!B47</f>
         <v/>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="23">
         <f>B6/Kevin模型!B22-1</f>
         <v/>
       </c>
@@ -606,7 +623,7 @@
         <f>Kevin模型!B48</f>
         <v/>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="23">
         <f>B7/Kevin模型!B22-1</f>
         <v/>
       </c>
@@ -626,7 +643,7 @@
         <f>Kevin模型!B49</f>
         <v/>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="23">
         <f>B8/Kevin模型!B22-1</f>
         <v/>
       </c>
@@ -645,7 +662,7 @@
       <c r="B9" s="6" t="n">
         <v>1500</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="23">
         <f>B9/Kevin模型!B22-1</f>
         <v/>
       </c>
@@ -664,7 +681,7 @@
       <c r="B10" s="6" t="n">
         <v>3500</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="23">
         <f>B10/Kevin模型!B22-1</f>
         <v/>
       </c>
@@ -703,6 +720,497 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>同業比較（2026-10-01；TTM=2025Q3–2026Q2；比率為 2026H1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>可比類型</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>幣別</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>收盤價</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>市值(億，原幣)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>TTM EPS</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>PE TTM</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>淨利率</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>H1營收YoY</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>8月營收YoY</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>1–8月YoY</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Q2 EPS YoY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TWSE:2345</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>10619.252</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>63.65</v>
+      </c>
+      <c r="H4" s="25">
+        <f>E4/G4</f>
+        <v/>
+      </c>
+      <c r="I4" s="26" t="n">
+        <v>15.35456010158373</v>
+      </c>
+      <c r="J4" s="27" t="n">
+        <v>0.1963200737820257</v>
+      </c>
+      <c r="K4" s="27" t="n">
+        <v>0.1169833478268205</v>
+      </c>
+      <c r="L4" s="28" t="n">
+        <v>0.6028812303772271</v>
+      </c>
+      <c r="M4" s="28" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>1.195338512763596</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Celestica</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>NYSE:CLS</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>完全可比</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>428.020495</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>9.719999999999999</v>
+      </c>
+      <c r="H5" s="25">
+        <f>E5/G5</f>
+        <v/>
+      </c>
+      <c r="I5" s="26" t="n">
+        <v>17.26437731892241</v>
+      </c>
+      <c r="J5" s="27" t="n">
+        <v>0.1160240578119283</v>
+      </c>
+      <c r="K5" s="27" t="n">
+        <v>0.06644484083424808</v>
+      </c>
+      <c r="L5" s="28" t="n">
+        <v>0.5780584626488632</v>
+      </c>
+      <c r="M5" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.7540983606557377</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Arista Networks</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>NYSE:ANET</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>替代可比</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>204.385</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>2573.55345586</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H6" s="25">
+        <f>E6/G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>17.38785598437595</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>0.6244190297143454</v>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>0.3891935175030898</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0.3646664766248575</v>
+      </c>
+      <c r="M6" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.352112676056338</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>TWSE:6285</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>相鄰可比</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1139.02805825</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>9.200000000000001</v>
+      </c>
+      <c r="H7" s="25">
+        <f>E7/G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>3.160171387908038</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>0.1295670101205102</v>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>0.04026044841196885</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>0.2280255126229542</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>0.8121</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>2.29126213592233</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>同業中位數</t>
+        </is>
+      </c>
+      <c r="H8" s="29">
+        <f>MEDIAN(H5:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="29">
+        <f>MEDIAN(I5:I7)</f>
+        <v/>
+      </c>
+      <c r="J8" s="30">
+        <f>MEDIAN(J5:J7)</f>
+        <v/>
+      </c>
+      <c r="K8" s="30">
+        <f>MEDIAN(K5:K7)</f>
+        <v/>
+      </c>
+      <c r="L8" s="31">
+        <f>MEDIAN(L5:L7)</f>
+        <v/>
+      </c>
+      <c r="O8" s="31">
+        <f>MEDIAN(O5:O7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>同業平均</t>
+        </is>
+      </c>
+      <c r="H9" s="29">
+        <f>AVERAGE(H5:H7)</f>
+        <v/>
+      </c>
+      <c r="I9" s="29">
+        <f>AVERAGE(I5:I7)</f>
+        <v/>
+      </c>
+      <c r="J9" s="30">
+        <f>AVERAGE(J5:J7)</f>
+        <v/>
+      </c>
+      <c r="K9" s="30">
+        <f>AVERAGE(K5:K7)</f>
+        <v/>
+      </c>
+      <c r="L9" s="31">
+        <f>AVERAGE(L5:L7)</f>
+        <v/>
+      </c>
+      <c r="O9" s="31">
+        <f>AVERAGE(O5:O7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>RelPE_TTM</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>H4/H8</f>
+        <v/>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>&lt;0.85 偏低；0.85–1.15 合理；&gt;1.15 偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>RelPE_FWD</t>
+        </is>
+      </c>
+      <c r="B12" s="32">
+        <f>Kevin模型!B22/Kevin模型!B37/H8</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>現價÷模型EPS ÷ 同業TTM中位</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>RelGM (pp)</t>
+        </is>
+      </c>
+      <c r="B13" s="33">
+        <f>(J4-J8)*100</f>
+        <v/>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>正值通常對應較高 PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Rel_RevGrowth (pp)</t>
+        </is>
+      </c>
+      <c r="B14" s="33">
+        <f>(L4-L8)*100</f>
+        <v/>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>H1 營收 YoY 差</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>綜合判斷</t>
+        </is>
+      </c>
+      <c r="B15" s="34">
+        <f>IF(AND(B11&lt;0.85,B13&gt;=0,B14&gt;=0),"相對偏低估",IF(AND(B11&gt;1.15,B13&lt;=0,B14&lt;=0),"相對偏高估","相對合理"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>來源：Bigdata.com company tearsheet（FMP，2026-10-01）；台股月營收：鉅亨網。美股無月營收標 N/A；營收成長統一用 2026H1 YoY。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -919,7 +1427,7 @@
           <t>業主淨利占比 W</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="35" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -995,7 +1503,7 @@
           <t>ETF PE（00891）</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="26" t="n">
         <v>28</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1292,11 +1800,11 @@
           <t>非經常性占稅前</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="36">
         <f>ABS(B11+B12)/B8</f>
         <v/>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="36">
         <f>ABS(B11+B12)/B8</f>
         <v/>
       </c>
@@ -1372,11 +1880,11 @@
           <t>EPS 成長率 O</t>
         </is>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="36">
         <f>B37/B16-1</f>
         <v/>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="36">
         <f>C37/B16-1</f>
         <v/>
       </c>
@@ -1492,11 +2000,11 @@
           <t>漲幅空間</t>
         </is>
       </c>
-      <c r="B44" s="21">
+      <c r="B44" s="37">
         <f>B43/B22-1</f>
         <v/>
       </c>
-      <c r="C44" s="21">
+      <c r="C44" s="37">
         <f>C43/B22-1</f>
         <v/>
       </c>
@@ -1512,11 +2020,11 @@
           <t>目前本益比 M/N</t>
         </is>
       </c>
-      <c r="B45" s="22">
+      <c r="B45" s="25">
         <f>B22/B37</f>
         <v/>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="25">
         <f>B22/C37</f>
         <v/>
       </c>
@@ -1685,7 +2193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1782,21 +2290,21 @@
       <c r="C2" s="6" t="n">
         <v>5608.73</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="36">
         <f>C2/B2</f>
         <v/>
       </c>
       <c r="E2" s="6" t="n">
         <v>3463.45</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="36">
         <f>E2/B2</f>
         <v/>
       </c>
       <c r="G2" s="6" t="n">
         <v>3308.727</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="23">
         <f>(G2-E2)/G2</f>
         <v/>
       </c>
@@ -1825,21 +2333,21 @@
       <c r="C3" s="6" t="n">
         <v>8064.689</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="36">
         <f>C3/B3</f>
         <v/>
       </c>
       <c r="E3" s="6" t="n">
         <v>5182.431</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="36">
         <f>E3/B3</f>
         <v/>
       </c>
       <c r="G3" s="6" t="n">
         <v>5659.005</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="23">
         <f>(G3-E3)/G3</f>
         <v/>
       </c>
@@ -1868,21 +2376,21 @@
       <c r="C4" s="6" t="n">
         <v>8647.449000000001</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="36">
         <f>C4/B4</f>
         <v/>
       </c>
       <c r="E4" s="6" t="n">
         <v>5947.219</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="36">
         <f>E4/B4</f>
         <v/>
       </c>
       <c r="G4" s="6" t="n">
         <v>6281.874</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="23">
         <f>(G4-E4)/G4</f>
         <v/>
       </c>
@@ -1911,21 +2419,21 @@
       <c r="C5" s="6" t="n">
         <v>10863.942</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="36">
         <f>C5/B5</f>
         <v/>
       </c>
       <c r="E5" s="6" t="n">
         <v>8125.282</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="36">
         <f>E5/B5</f>
         <v/>
       </c>
       <c r="G5" s="6" t="n">
         <v>6613.117</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="23">
         <f>(G5-E5)/G5</f>
         <v/>
       </c>
@@ -1954,21 +2462,21 @@
       <c r="C6" s="6" t="n">
         <v>12315.464</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="36">
         <f>C6/B6</f>
         <v/>
       </c>
       <c r="E6" s="6" t="n">
         <v>9000.709999999999</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="36">
         <f>E6/B6</f>
         <v/>
       </c>
       <c r="G6" s="6" t="n">
         <v>9707.726000000001</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="23">
         <f>(G6-E6)/G6</f>
         <v/>
       </c>
@@ -1997,21 +2505,21 @@
       <c r="C7" s="6" t="n">
         <v>12909.713</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="36">
         <f>C7/B7</f>
         <v/>
       </c>
       <c r="E7" s="6" t="n">
         <v>9165.174999999999</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="36">
         <f>E7/B7</f>
         <v/>
       </c>
       <c r="G7" s="6" t="n">
         <v>10314.141</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="23">
         <f>(G7-E7)/G7</f>
         <v/>
       </c>
@@ -2040,21 +2548,21 @@
       <c r="C8" s="6" t="n">
         <v>13700.875</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="36">
         <f>C8/B8</f>
         <v/>
       </c>
       <c r="E8" s="6" t="n">
         <v>10048.687</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="36">
         <f>E8/B8</f>
         <v/>
       </c>
       <c r="G8" s="6" t="n">
         <v>10361.703</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="23">
         <f>(G8-E8)/G8</f>
         <v/>
       </c>
@@ -2083,21 +2591,21 @@
       <c r="C9" s="6" t="n">
         <v>18822.758</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="36">
         <f>C9/B9</f>
         <v/>
       </c>
       <c r="E9" s="6" t="n">
         <v>14331.32</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="36">
         <f>E9/B9</f>
         <v/>
       </c>
       <c r="G9" s="6" t="n">
         <v>14568.367</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="23">
         <f>(G9-E9)/G9</f>
         <v/>
       </c>
@@ -2126,7 +2634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
